--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الاقتصاد والتمويل_طلاب.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الاقتصاد والتمويل_طلاب.xlsx
@@ -32,9 +32,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
   <fonts count="1">
     <font>
       <sz val="12"/>
@@ -464,7 +461,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="str">
-        <v>د. أشرف الحاج</v>
+        <v>اشرف كمال عثمان ابراهيم</v>
       </c>
       <c r="C4" t="str">
         <v>80</v>
@@ -484,7 +481,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="str">
-        <v>د. أشرف كمال عثمان</v>
+        <v>اشرف كمال عثمان ابراهيم</v>
       </c>
       <c r="C5" t="str">
         <v>80</v>
@@ -504,7 +501,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="str">
-        <v>د. الصادق الطيب</v>
+        <v>بشير بكرى عجيب بابكر</v>
       </c>
       <c r="C6" t="str">
         <v>85</v>
@@ -524,7 +521,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="str">
-        <v>د. حاتم حسن</v>
+        <v>حاتم حسن ضيف الله سعيد</v>
       </c>
       <c r="C7" t="str">
         <v>64</v>
@@ -544,7 +541,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="str">
-        <v>د. حامد الخواجة</v>
+        <v>خالد محمد قرني البدوي</v>
       </c>
       <c r="C8" t="str">
         <v>88</v>
@@ -584,7 +581,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="str">
-        <v>د. عماد باشهاب</v>
+        <v>عماد علي ابراهيم باشهاب</v>
       </c>
       <c r="C10" t="str">
         <v>63 ومكتب رئيس القسم</v>
@@ -604,7 +601,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="str">
-        <v>د. محمد المطرفي</v>
+        <v>محمد تركي حامد المطرفي</v>
       </c>
       <c r="C11" t="str">
         <v>71</v>
@@ -624,7 +621,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="str">
-        <v>د. محمود عبد العال مشعال</v>
+        <v>محمود عبد العال محمد مشعال</v>
       </c>
       <c r="C12" t="str">
         <v>86</v>
@@ -644,7 +641,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="str">
-        <v>د. مهند جعفر حسن حبيب</v>
+        <v>مهند جعفر حسن حبيب</v>
       </c>
       <c r="C13" t="str">
         <v>73</v>
@@ -664,7 +661,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="str">
-        <v>د. وائل محمود علي</v>
+        <v>وائل محمود علي محمد</v>
       </c>
       <c r="C14" t="str">
         <v>70</v>
@@ -684,7 +681,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="str">
-        <v>د/ محمد سعد محمود عبد الرحيم</v>
+        <v>محمد سعد محمود عبد الرحيم</v>
       </c>
       <c r="C15" t="str">
         <v>62</v>
@@ -704,7 +701,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="str">
-        <v>أ. أحمد سجحي</v>
+        <v>فائز عباد عريج الشاطري المطيري</v>
       </c>
       <c r="C16" t="str">
         <v>79</v>
@@ -724,7 +721,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="str">
-        <v>أ. خالد الغامدي</v>
+        <v>خالد احمد مسفر القشيري الغامدي</v>
       </c>
       <c r="C17" t="str">
         <v>87</v>
@@ -764,7 +761,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="str">
-        <v>د. أيمن بازهير</v>
+        <v>ايمن حسن سعيد بازهير</v>
       </c>
       <c r="C19" t="str">
         <v>77</v>
@@ -784,7 +781,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="str">
-        <v>د. خالد البدوي</v>
+        <v>خالد محمد قرني البدوي</v>
       </c>
       <c r="C20" t="str">
         <v>88</v>
@@ -804,7 +801,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="str">
-        <v>د. يزيد عبدالعزيز آل ناجي</v>
+        <v>يزيد عبدالعزيز حسين آل ناجي</v>
       </c>
       <c r="C21" t="str">
         <v>72</v>

--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الاقتصاد والتمويل_طلاب.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الاقتصاد والتمويل_طلاب.xlsx
@@ -461,7 +461,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="str">
-        <v>اشرف كمال عثمان ابراهيم</v>
+        <v>اشرف حسن احمد الحاج</v>
       </c>
       <c r="C4" t="str">
         <v>80</v>
@@ -501,7 +501,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="str">
-        <v>بشير بكرى عجيب بابكر</v>
+        <v>الصادق محمد سالم الطيب</v>
       </c>
       <c r="C6" t="str">
         <v>85</v>
@@ -541,7 +541,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="str">
-        <v>خالد محمد قرني البدوي</v>
+        <v>حامد عبدالقوي محمد الخواجه</v>
       </c>
       <c r="C8" t="str">
         <v>88</v>
@@ -561,7 +561,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="str">
-        <v>د. ساير الجعيد</v>
+        <v>ساير ساعد ساير الجعيد</v>
       </c>
       <c r="C9" t="str">
         <v>81</v>
@@ -641,7 +641,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="str">
-        <v>مهند جعفر حسن حبيب</v>
+        <v>د. مهند جعفر حسن حبيب</v>
       </c>
       <c r="C13" t="str">
         <v>73</v>
@@ -681,7 +681,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="str">
-        <v>محمد سعد محمود عبد الرحيم</v>
+        <v>د/ محمد سعد محمود عبد الرحيم</v>
       </c>
       <c r="C15" t="str">
         <v>62</v>
@@ -701,7 +701,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="str">
-        <v>فائز عباد عريج الشاطري المطيري</v>
+        <v>أ. أحمد سجحي</v>
       </c>
       <c r="C16" t="str">
         <v>79</v>

--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الاقتصاد والتمويل_طلاب.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الاقتصاد والتمويل_طلاب.xlsx
@@ -741,7 +741,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="str">
-        <v>أ. فايز المطيري</v>
+        <v>فائز عباد عريج الشاطري المطيري</v>
       </c>
       <c r="C18" t="str">
         <v>مبنى 5000</v>

--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الاقتصاد والتمويل_طلاب.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الاقتصاد والتمويل_طلاب.xlsx
@@ -394,7 +394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -701,7 +701,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="str">
-        <v>أ. أحمد سجحي</v>
+        <v>احمد حسين احمد سبحي</v>
       </c>
       <c r="C16" t="str">
         <v>79</v>
@@ -836,29 +836,9 @@
         <v>الفترة الأولى</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23">
-        <v>20</v>
-      </c>
-      <c r="B23" t="str">
-        <v>احمد حسين احمد سبحي</v>
-      </c>
-      <c r="C23" t="str">
-        <v/>
-      </c>
-      <c r="D23" t="str">
-        <v>الفترة الأولى</v>
-      </c>
-      <c r="E23" t="str">
-        <v>الفترة الثانية</v>
-      </c>
-      <c r="F23" t="str">
-        <v>الفترة الأولى</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الاقتصاد والتمويل_طلاب.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الاقتصاد والتمويل_طلاب.xlsx
@@ -504,7 +504,7 @@
         <v>الصادق محمد سالم الطيب</v>
       </c>
       <c r="C6" t="str">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D6" t="str">
         <v>الفترة الأولى</v>
@@ -564,7 +564,7 @@
         <v>ساير ساعد ساير الجعيد</v>
       </c>
       <c r="C9" t="str">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D9" t="str">
         <v>الفترة الأولى</v>
@@ -584,7 +584,7 @@
         <v>عماد علي ابراهيم باشهاب</v>
       </c>
       <c r="C10" t="str">
-        <v>63 ومكتب رئيس القسم</v>
+        <v>63</v>
       </c>
       <c r="D10" t="str">
         <v>الفترة الأولى</v>
@@ -744,7 +744,7 @@
         <v>فائز عباد عريج الشاطري المطيري</v>
       </c>
       <c r="C18" t="str">
-        <v>مبنى 5000</v>
+        <v>79</v>
       </c>
       <c r="D18" t="str">
         <v>الفترة الثانية</v>
